--- a/AAII_Financials/Yearly/PTKFY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PTKFY_YR_FIN.xlsx
@@ -927,7 +927,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>45900</v>
+        <v>45100</v>
       </c>
       <c r="E15" s="3">
         <v>44500</v>
@@ -1086,7 +1086,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>321100</v>
+        <v>320300</v>
       </c>
       <c r="E21" s="3">
         <v>301600</v>
